--- a/data/gravel/Bearclaw Thunderhawk 2025.xlsx
+++ b/data/gravel/Bearclaw Thunderhawk 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10713"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10727"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B28C29B8-5663-D249-83B3-35AA9B79C11F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8E5FD68-E9A0-114D-90A9-02A4307485AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2880" yWindow="4080" windowWidth="26100" windowHeight="15400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2700" yWindow="2600" windowWidth="26100" windowHeight="15400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -399,12 +399,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1231,7 +1230,7 @@
       <c r="A24" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B24" s="4"/>
+      <c r="B24" s="3"/>
       <c r="C24" s="1"/>
       <c r="D24" s="1"/>
       <c r="E24" s="1"/>
@@ -1245,7 +1244,7 @@
       <c r="A25" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B25" s="4"/>
+      <c r="B25" s="3"/>
       <c r="C25" s="1"/>
       <c r="D25" s="1"/>
       <c r="E25" s="1"/>
@@ -1585,25 +1584,25 @@
       <c r="B37" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="C37" s="4" t="s">
+      <c r="C37" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="D37" s="4" t="s">
+      <c r="D37" s="3" t="s">
         <v>92</v>
       </c>
       <c r="E37" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="F37" s="4" t="s">
+      <c r="F37" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="G37" s="4" t="s">
+      <c r="G37" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="H37" s="4" t="s">
+      <c r="H37" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="I37" s="4" t="s">
+      <c r="I37" s="3" t="s">
         <v>104</v>
       </c>
       <c r="J37" s="3" t="s">
@@ -1677,7 +1676,7 @@
         <v>39</v>
       </c>
       <c r="B42" s="1">
-        <v>60</v>
+        <v>2.35</v>
       </c>
       <c r="C42" s="1"/>
       <c r="D42" s="1"/>
@@ -1710,10 +1709,10 @@
       <c r="C44" s="1"/>
       <c r="D44" s="1"/>
       <c r="E44" s="3"/>
-      <c r="F44" s="4"/>
-      <c r="G44" s="4"/>
-      <c r="H44" s="4"/>
-      <c r="I44" s="4"/>
+      <c r="F44" s="3"/>
+      <c r="G44" s="3"/>
+      <c r="H44" s="3"/>
+      <c r="I44" s="3"/>
       <c r="J44" s="1"/>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.3">
@@ -1721,8 +1720,8 @@
         <v>42</v>
       </c>
       <c r="B45" s="1"/>
-      <c r="C45" s="4"/>
-      <c r="D45" s="4"/>
+      <c r="C45" s="3"/>
+      <c r="D45" s="3"/>
       <c r="E45" s="1"/>
       <c r="F45" s="1"/>
       <c r="G45" s="1"/>

--- a/data/gravel/Bearclaw Thunderhawk 2025.xlsx
+++ b/data/gravel/Bearclaw Thunderhawk 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10727"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8E5FD68-E9A0-114D-90A9-02A4307485AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFE7026B-854A-BF4E-BF55-B390E1501864}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2700" yWindow="2600" windowWidth="26100" windowHeight="15400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="108">
   <si>
     <t>brand</t>
   </si>
@@ -354,6 +354,9 @@
   </si>
   <si>
     <t>https://bearclawbicycleco.com/pages/thunderhawk</t>
+  </si>
+  <si>
+    <t>https://cdn.shopify.com/s/files/1/0850/1320/1198/files/Thunderhawk_Titanium_Gravel_Bike_UDH_Red_Transmission.jpg?v=1736993270</t>
   </si>
 </sst>
 </file>
@@ -746,6 +749,11 @@
         <v>106</v>
       </c>
     </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B6" t="s">
+        <v>107</v>
+      </c>
+    </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>6</v>

--- a/data/gravel/Bearclaw Thunderhawk 2025.xlsx
+++ b/data/gravel/Bearclaw Thunderhawk 2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFE7026B-854A-BF4E-BF55-B390E1501864}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8AD3396-873D-2146-9570-5D8B5CFF585D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2700" yWindow="2600" windowWidth="26100" windowHeight="15400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="110">
   <si>
     <t>brand</t>
   </si>
@@ -357,6 +357,12 @@
   </si>
   <si>
     <t>https://cdn.shopify.com/s/files/1/0850/1320/1198/files/Thunderhawk_Titanium_Gravel_Bike_UDH_Red_Transmission.jpg?v=1736993270</t>
+  </si>
+  <si>
+    <t>location</t>
+  </si>
+  <si>
+    <t>Dexter, Michigan, USA</t>
   </si>
 </sst>
 </file>
@@ -703,7 +709,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J72"/>
+  <dimension ref="A1:J73"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -2153,6 +2159,14 @@
       <c r="I72" s="1"/>
       <c r="J72" s="1"/>
     </row>
+    <row r="73" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
+        <v>108</v>
+      </c>
+      <c r="B73" t="s">
+        <v>109</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/data/gravel/Bearclaw Thunderhawk 2025.xlsx
+++ b/data/gravel/Bearclaw Thunderhawk 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8AD3396-873D-2146-9570-5D8B5CFF585D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25F95369-59B1-F84D-A96E-FA741571FB59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2700" yWindow="2600" windowWidth="26100" windowHeight="15400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="116">
   <si>
     <t>brand</t>
   </si>
@@ -363,6 +363,24 @@
   </si>
   <si>
     <t>Dexter, Michigan, USA</t>
+  </si>
+  <si>
+    <t>head_tube_d</t>
+  </si>
+  <si>
+    <t>headset_upper</t>
+  </si>
+  <si>
+    <t>headset_lower</t>
+  </si>
+  <si>
+    <t>fork_steerer</t>
+  </si>
+  <si>
+    <t>fork_steerer_d</t>
+  </si>
+  <si>
+    <t>fork_material</t>
   </si>
 </sst>
 </file>
@@ -709,7 +727,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J73"/>
+  <dimension ref="A1:J79"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -1791,11 +1809,9 @@
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A49" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>98</v>
-      </c>
+        <v>110</v>
+      </c>
+      <c r="B49" s="1"/>
       <c r="C49" s="1"/>
       <c r="D49" s="1"/>
       <c r="E49" s="1"/>
@@ -1807,7 +1823,7 @@
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A50" s="1" t="s">
-        <v>47</v>
+        <v>111</v>
       </c>
       <c r="B50" s="1"/>
       <c r="C50" s="1"/>
@@ -1821,11 +1837,9 @@
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A51" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="B51" s="1">
-        <v>31.6</v>
-      </c>
+        <v>112</v>
+      </c>
+      <c r="B51" s="1"/>
       <c r="C51" s="1"/>
       <c r="D51" s="1"/>
       <c r="E51" s="1"/>
@@ -1837,11 +1851,9 @@
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A52" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="B52" s="1" t="s">
-        <v>76</v>
-      </c>
+        <v>113</v>
+      </c>
+      <c r="B52" s="1"/>
       <c r="C52" s="1"/>
       <c r="D52" s="1"/>
       <c r="E52" s="1"/>
@@ -1853,11 +1865,9 @@
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="B53" s="1">
-        <v>50</v>
-      </c>
+        <v>114</v>
+      </c>
+      <c r="B53" s="1"/>
       <c r="C53" s="1"/>
       <c r="D53" s="1"/>
       <c r="E53" s="1"/>
@@ -1869,11 +1879,9 @@
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="B54" s="1" t="s">
-        <v>99</v>
-      </c>
+        <v>115</v>
+      </c>
+      <c r="B54" s="1"/>
       <c r="C54" s="1"/>
       <c r="D54" s="1"/>
       <c r="E54" s="1"/>
@@ -1885,9 +1893,11 @@
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="B55" s="1"/>
+        <v>46</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>98</v>
+      </c>
       <c r="C55" s="1"/>
       <c r="D55" s="1"/>
       <c r="E55" s="1"/>
@@ -1899,11 +1909,9 @@
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A56" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="B56" s="1">
-        <v>140</v>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="B56" s="1"/>
       <c r="C56" s="1"/>
       <c r="D56" s="1"/>
       <c r="E56" s="1"/>
@@ -1915,9 +1923,11 @@
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A57" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="B57" s="1"/>
+        <v>48</v>
+      </c>
+      <c r="B57" s="1">
+        <v>31.6</v>
+      </c>
       <c r="C57" s="1"/>
       <c r="D57" s="1"/>
       <c r="E57" s="1"/>
@@ -1929,10 +1939,10 @@
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A58" s="1" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C58" s="1"/>
       <c r="D58" s="1"/>
@@ -1945,10 +1955,10 @@
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A59" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="B59" s="1" t="s">
-        <v>77</v>
+        <v>50</v>
+      </c>
+      <c r="B59" s="1">
+        <v>50</v>
       </c>
       <c r="C59" s="1"/>
       <c r="D59" s="1"/>
@@ -1961,9 +1971,11 @@
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A60" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="B60" s="1"/>
+        <v>51</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>99</v>
+      </c>
       <c r="C60" s="1"/>
       <c r="D60" s="1"/>
       <c r="E60" s="1"/>
@@ -1975,7 +1987,7 @@
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A61" s="1" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="B61" s="1"/>
       <c r="C61" s="1"/>
@@ -1989,10 +2001,10 @@
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A62" s="1" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="B62" s="1">
-        <v>2</v>
+        <v>140</v>
       </c>
       <c r="C62" s="1"/>
       <c r="D62" s="1"/>
@@ -2005,11 +2017,9 @@
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A63" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="B63" s="1">
-        <v>1</v>
-      </c>
+        <v>54</v>
+      </c>
+      <c r="B63" s="1"/>
       <c r="C63" s="1"/>
       <c r="D63" s="1"/>
       <c r="E63" s="1"/>
@@ -2021,9 +2031,11 @@
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A64" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="B64" s="1"/>
+        <v>55</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>77</v>
+      </c>
       <c r="C64" s="1"/>
       <c r="D64" s="1"/>
       <c r="E64" s="1"/>
@@ -2035,10 +2047,10 @@
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A65" s="1" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C65" s="1"/>
       <c r="D65" s="1"/>
@@ -2051,7 +2063,7 @@
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A66" s="1" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="B66" s="1"/>
       <c r="C66" s="1"/>
@@ -2065,11 +2077,9 @@
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A67" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="B67" s="1" t="s">
-        <v>76</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="B67" s="1"/>
       <c r="C67" s="1"/>
       <c r="D67" s="1"/>
       <c r="E67" s="1"/>
@@ -2081,10 +2091,10 @@
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A68" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="B68" s="1" t="s">
-        <v>76</v>
+        <v>59</v>
+      </c>
+      <c r="B68" s="1">
+        <v>2</v>
       </c>
       <c r="C68" s="1"/>
       <c r="D68" s="1"/>
@@ -2097,10 +2107,10 @@
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A69" s="1" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="B69" s="1">
-        <v>2490</v>
+        <v>1</v>
       </c>
       <c r="C69" s="1"/>
       <c r="D69" s="1"/>
@@ -2113,11 +2123,9 @@
     </row>
     <row r="70" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A70" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="B70" s="1">
-        <v>6390</v>
-      </c>
+        <v>61</v>
+      </c>
+      <c r="B70" s="1"/>
       <c r="C70" s="1"/>
       <c r="D70" s="1"/>
       <c r="E70" s="1"/>
@@ -2129,7 +2137,7 @@
     </row>
     <row r="71" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A71" s="1" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="B71" s="1" t="s">
         <v>76</v>
@@ -2145,11 +2153,9 @@
     </row>
     <row r="72" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A72" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="B72" s="1" t="s">
-        <v>96</v>
-      </c>
+        <v>63</v>
+      </c>
+      <c r="B72" s="1"/>
       <c r="C72" s="1"/>
       <c r="D72" s="1"/>
       <c r="E72" s="1"/>
@@ -2160,10 +2166,106 @@
       <c r="J72" s="1"/>
     </row>
     <row r="73" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A73" t="s">
+      <c r="A73" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C73" s="1"/>
+      <c r="D73" s="1"/>
+      <c r="E73" s="1"/>
+      <c r="F73" s="1"/>
+      <c r="G73" s="1"/>
+      <c r="H73" s="1"/>
+      <c r="I73" s="1"/>
+      <c r="J73" s="1"/>
+    </row>
+    <row r="74" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A74" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C74" s="1"/>
+      <c r="D74" s="1"/>
+      <c r="E74" s="1"/>
+      <c r="F74" s="1"/>
+      <c r="G74" s="1"/>
+      <c r="H74" s="1"/>
+      <c r="I74" s="1"/>
+      <c r="J74" s="1"/>
+    </row>
+    <row r="75" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A75" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B75" s="1">
+        <v>2490</v>
+      </c>
+      <c r="C75" s="1"/>
+      <c r="D75" s="1"/>
+      <c r="E75" s="1"/>
+      <c r="F75" s="1"/>
+      <c r="G75" s="1"/>
+      <c r="H75" s="1"/>
+      <c r="I75" s="1"/>
+      <c r="J75" s="1"/>
+    </row>
+    <row r="76" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A76" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B76" s="1">
+        <v>6390</v>
+      </c>
+      <c r="C76" s="1"/>
+      <c r="D76" s="1"/>
+      <c r="E76" s="1"/>
+      <c r="F76" s="1"/>
+      <c r="G76" s="1"/>
+      <c r="H76" s="1"/>
+      <c r="I76" s="1"/>
+      <c r="J76" s="1"/>
+    </row>
+    <row r="77" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A77" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C77" s="1"/>
+      <c r="D77" s="1"/>
+      <c r="E77" s="1"/>
+      <c r="F77" s="1"/>
+      <c r="G77" s="1"/>
+      <c r="H77" s="1"/>
+      <c r="I77" s="1"/>
+      <c r="J77" s="1"/>
+    </row>
+    <row r="78" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A78" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="C78" s="1"/>
+      <c r="D78" s="1"/>
+      <c r="E78" s="1"/>
+      <c r="F78" s="1"/>
+      <c r="G78" s="1"/>
+      <c r="H78" s="1"/>
+      <c r="I78" s="1"/>
+      <c r="J78" s="1"/>
+    </row>
+    <row r="79" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
         <v>108</v>
       </c>
-      <c r="B73" t="s">
+      <c r="B79" t="s">
         <v>109</v>
       </c>
     </row>
